--- a/bolao_atual.xlsx
+++ b/bolao_atual.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a81d17a7f6589cb1/Python projects/Bolão/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF6DA5F2-DAC5-4A4E-BA59-00D82C013C18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{DF6DA5F2-DAC5-4A4E-BA59-00D82C013C18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A8C6D6D-B5A5-48E1-B03F-F8C90CF2036A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6E2B9C0F-DA98-462E-9B39-99169BF1CE84}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{6E2B9C0F-DA98-462E-9B39-99169BF1CE84}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="91">
   <si>
     <t xml:space="preserve">Fláviana Roziriz </t>
   </si>
@@ -703,7 +703,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E6D8180-E21A-492C-893E-09CB01200710}">
-  <dimension ref="A1:B47"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="26.44140625" bestFit="1" customWidth="1"/>
@@ -1070,18 +1070,10 @@
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" s="3" t="s">
+      <c r="A46" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B46" s="3" t="s">
         <v>88</v>
       </c>
     </row>

--- a/bolao_atual.xlsx
+++ b/bolao_atual.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a81d17a7f6589cb1/Python projects/Bolão/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{DF6DA5F2-DAC5-4A4E-BA59-00D82C013C18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79450A2F-541F-405E-881D-894E2A7B60FE}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{DF6DA5F2-DAC5-4A4E-BA59-00D82C013C18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C41BBE8A-1D06-4CC2-ABA9-5BC6F0F86B7E}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6E2B9C0F-DA98-462E-9B39-99169BF1CE84}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{6E2B9C0F-DA98-462E-9B39-99169BF1CE84}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -197,160 +197,160 @@
     <t>Benildo</t>
   </si>
   <si>
-    <t>1;2;3;4;5;20;30;40;50;60</t>
-  </si>
-  <si>
-    <t>1;2;3;12;13;16;20;22;50;53</t>
-  </si>
-  <si>
-    <t>3;7;11;17;19;20;23;28;33;59</t>
-  </si>
-  <si>
-    <t>3;10;16;18;26;28;32;37;55;58</t>
-  </si>
-  <si>
-    <t>3;7;14;17;19;27;36;41;52;54</t>
-  </si>
-  <si>
-    <t>6;7;10;18;25;29;49;52;56;60</t>
-  </si>
-  <si>
-    <t>1;7;13;18;22;23;27;45;52;59</t>
-  </si>
-  <si>
-    <t>7;10;14;23;32;35;46;51;54;57</t>
-  </si>
-  <si>
-    <t>8;12;19;28;31;36;39;42;46;53</t>
-  </si>
-  <si>
-    <t>8;10;13;17;31;38;45;54;57;60</t>
-  </si>
-  <si>
-    <t>5;7;8;12;13;19;21;22;41;43</t>
-  </si>
-  <si>
-    <t>2;7;10;18;22;26;36;44;46;52</t>
-  </si>
-  <si>
-    <t>3;7;14;18;28;37;54;56;58;59</t>
-  </si>
-  <si>
-    <t>1;3;5;7;9;11;13;15;17;31</t>
-  </si>
-  <si>
-    <t>11;13;17;18;23;24;33;36;47;49</t>
-  </si>
-  <si>
-    <t>4;10;14;17;20;26;34;46;54;57</t>
-  </si>
-  <si>
-    <t>5;11;17;23;32;33;34;42;44;57</t>
-  </si>
-  <si>
-    <t>1;5;8;11;23;28;30;32;38;53</t>
-  </si>
-  <si>
-    <t>3;9;14;17;27;31;38;40;51;59</t>
-  </si>
-  <si>
-    <t>4;8;10;14;16;21;25;26;40;54</t>
-  </si>
-  <si>
-    <t>3;4;7;10;30;40;48;50;54;58</t>
-  </si>
-  <si>
-    <t>2;10;14;16;21;25;35;44;55;60</t>
-  </si>
-  <si>
-    <t>5;10;18;19;22;25;28;39;44;50</t>
-  </si>
-  <si>
-    <t>2;6;15;17;20;26;39;43;44;57</t>
-  </si>
-  <si>
-    <t>3;9;11;22;27;31;38;44;50;51</t>
-  </si>
-  <si>
-    <t>5;16;19;21;30;37;45;48;55;58</t>
-  </si>
-  <si>
-    <t>2;5;10;17;25;33;35;45;50;51</t>
-  </si>
-  <si>
-    <t>6;11;15;16;19;25;37;50;52;59</t>
-  </si>
-  <si>
-    <t>1;6;10;14;15;21;41;44;53;57</t>
-  </si>
-  <si>
-    <t>3;4;16;19;31;34;39;40;45;48</t>
-  </si>
-  <si>
-    <t>2;4;16;17;19;20;21;22;40;50</t>
-  </si>
-  <si>
-    <t>17;18;23;25;26;32;34;39;42;54</t>
-  </si>
-  <si>
-    <t>10;12;15;17;20;24;28;30;32;50</t>
-  </si>
-  <si>
-    <t>1;9;13;25;28;32;34;45;54;59</t>
-  </si>
-  <si>
-    <t>1;3;9;19;25;26;34;41;45;54</t>
-  </si>
-  <si>
-    <t>10;15;17;21;23;26;35;41;48;55</t>
-  </si>
-  <si>
-    <t>2;7;11;13;17;19;28;47;48;55</t>
-  </si>
-  <si>
-    <t>5;9;17;24;33;42;46;51;54;58</t>
-  </si>
-  <si>
-    <t>3;6;9;10;17;23;29;36;43;58</t>
-  </si>
-  <si>
-    <t>5;10;27;30;32;33;34;35;37;39</t>
-  </si>
-  <si>
-    <t>8;10;15;18;21;32;36;41;51;54</t>
-  </si>
-  <si>
-    <t>13;16;19;22;28;31;36;47;52;54</t>
-  </si>
-  <si>
-    <t>7;9;19;25;28;32;37;45;56;59</t>
-  </si>
-  <si>
-    <t>23;25;28;32;33;35;45;46;53;55</t>
-  </si>
-  <si>
-    <t>1;3;4;7;18;22;23;27;33;60</t>
-  </si>
-  <si>
-    <t>3;7;11;14;18;22;26;36;39;49</t>
-  </si>
-  <si>
-    <t>13;14;17;19;20;22;28;33;52;54</t>
-  </si>
-  <si>
-    <t>5;7;11;17;19;22;35;44;47;49</t>
-  </si>
-  <si>
-    <t>10;11;19;25;27;32;38;44;51;54</t>
-  </si>
-  <si>
-    <t>10;11;12;15;17;19;23;27;28;30</t>
-  </si>
-  <si>
-    <t>9;14;17;33;42;46;52;55;56;59</t>
-  </si>
-  <si>
-    <t>5;10;27;30;32;33;37;38;42;53</t>
+    <t>1,2,3,4,5,20,30,40,50,60</t>
+  </si>
+  <si>
+    <t>1,2,3,12,13,16,20,22,50,53</t>
+  </si>
+  <si>
+    <t>3,7,11,17,19,20,23,28,33,59</t>
+  </si>
+  <si>
+    <t>3,10,16,18,26,28,32,37,55,58</t>
+  </si>
+  <si>
+    <t>3,7,14,17,19,27,36,41,52,54</t>
+  </si>
+  <si>
+    <t>6,7,10,18,25,29,49,52,56,60</t>
+  </si>
+  <si>
+    <t>1,7,13,18,22,23,27,45,52,59</t>
+  </si>
+  <si>
+    <t>7,10,14,23,32,35,46,51,54,57</t>
+  </si>
+  <si>
+    <t>8,12,19,28,31,36,39,42,46,53</t>
+  </si>
+  <si>
+    <t>8,10,13,17,31,38,45,54,57,60</t>
+  </si>
+  <si>
+    <t>5,7,8,12,13,19,21,22,41,43</t>
+  </si>
+  <si>
+    <t>2,7,10,18,22,26,36,44,46,52</t>
+  </si>
+  <si>
+    <t>3,7,14,18,28,37,54,56,58,59</t>
+  </si>
+  <si>
+    <t>1,3,5,7,9,11,13,15,17,31</t>
+  </si>
+  <si>
+    <t>11,13,17,18,23,24,33,36,47,49</t>
+  </si>
+  <si>
+    <t>4,10,14,17,20,26,34,46,54,57</t>
+  </si>
+  <si>
+    <t>5,11,17,23,32,33,34,42,44,57</t>
+  </si>
+  <si>
+    <t>1,5,8,11,23,28,30,32,38,53</t>
+  </si>
+  <si>
+    <t>3,9,14,17,27,31,38,40,51,59</t>
+  </si>
+  <si>
+    <t>4,8,10,14,16,21,25,26,40,54</t>
+  </si>
+  <si>
+    <t>3,4,7,10,30,40,48,50,54,58</t>
+  </si>
+  <si>
+    <t>2,10,14,16,21,25,35,44,55,60</t>
+  </si>
+  <si>
+    <t>5,10,18,19,22,25,28,39,44,50</t>
+  </si>
+  <si>
+    <t>2,6,15,17,20,26,39,43,44,57</t>
+  </si>
+  <si>
+    <t>3,9,11,22,27,31,38,44,50,51</t>
+  </si>
+  <si>
+    <t>5,16,19,21,30,37,45,48,55,58</t>
+  </si>
+  <si>
+    <t>2,5,10,17,25,33,35,45,50,51</t>
+  </si>
+  <si>
+    <t>6,11,15,16,19,25,37,50,52,59</t>
+  </si>
+  <si>
+    <t>1,6,10,14,15,21,41,44,53,57</t>
+  </si>
+  <si>
+    <t>3,4,16,19,31,34,39,40,45,48</t>
+  </si>
+  <si>
+    <t>2,4,16,17,19,20,21,22,40,50</t>
+  </si>
+  <si>
+    <t>17,18,23,25,26,32,34,39,42,54</t>
+  </si>
+  <si>
+    <t>10,12,15,17,20,24,28,30,32,50</t>
+  </si>
+  <si>
+    <t>1,9,13,25,28,32,34,45,54,59</t>
+  </si>
+  <si>
+    <t>1,3,9,19,25,26,34,41,45,54</t>
+  </si>
+  <si>
+    <t>10,15,17,21,23,26,35,41,48,55</t>
+  </si>
+  <si>
+    <t>2,7,11,13,17,19,28,47,48,55</t>
+  </si>
+  <si>
+    <t>5,9,17,24,33,42,46,51,54,58</t>
+  </si>
+  <si>
+    <t>3,6,9,10,17,23,29,36,43,58</t>
+  </si>
+  <si>
+    <t>5,10,27,30,32,33,34,35,37,39</t>
+  </si>
+  <si>
+    <t>8,10,15,18,21,32,36,41,51,54</t>
+  </si>
+  <si>
+    <t>13,16,19,22,28,31,36,47,52,54</t>
+  </si>
+  <si>
+    <t>7,9,19,25,28,32,37,45,56,59</t>
+  </si>
+  <si>
+    <t>23,25,28,32,33,35,45,46,53,55</t>
+  </si>
+  <si>
+    <t>1,3,4,7,18,22,23,27,33,60</t>
+  </si>
+  <si>
+    <t>3,7,11,14,18,22,26,36,39,49</t>
+  </si>
+  <si>
+    <t>13,14,17,19,20,22,28,33,52,54</t>
+  </si>
+  <si>
+    <t>5,7,11,17,19,22,35,44,47,49</t>
+  </si>
+  <si>
+    <t>10,11,19,25,27,32,38,44,51,54</t>
+  </si>
+  <si>
+    <t>10,11,12,15,17,19,23,27,28,30</t>
+  </si>
+  <si>
+    <t>9,14,17,33,42,46,52,55,56,59</t>
+  </si>
+  <si>
+    <t>5,10,27,30,32,33,37,38,42,53</t>
   </si>
 </sst>
 </file>
@@ -423,10 +423,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -747,13 +743,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E6D8180-E21A-492C-893E-09CB01200710}">
   <dimension ref="A1:B53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>31</v>
       </c>
@@ -761,7 +757,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -769,7 +765,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -777,7 +773,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>33</v>
       </c>
@@ -785,7 +781,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>1</v>
       </c>
@@ -793,7 +789,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>34</v>
       </c>
@@ -801,7 +797,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>2</v>
       </c>
@@ -809,7 +805,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
@@ -817,7 +813,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>4</v>
       </c>
@@ -825,7 +821,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
@@ -833,7 +829,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>6</v>
       </c>
@@ -841,7 +837,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
@@ -849,7 +845,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>17</v>
       </c>
@@ -857,7 +853,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>9</v>
       </c>
@@ -865,7 +861,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>35</v>
       </c>
@@ -873,7 +869,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>10</v>
       </c>
@@ -881,7 +877,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>36</v>
       </c>
@@ -889,7 +885,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>37</v>
       </c>
@@ -897,7 +893,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>11</v>
       </c>
@@ -905,7 +901,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>13</v>
       </c>
@@ -913,7 +909,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>18</v>
       </c>
@@ -921,7 +917,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>19</v>
       </c>
@@ -929,7 +925,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>20</v>
       </c>
@@ -937,7 +933,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>21</v>
       </c>
@@ -945,7 +941,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>22</v>
       </c>
@@ -953,7 +949,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>23</v>
       </c>
@@ -961,7 +957,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>24</v>
       </c>
@@ -969,7 +965,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>25</v>
       </c>
@@ -977,7 +973,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>38</v>
       </c>
@@ -985,7 +981,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>26</v>
       </c>
@@ -993,7 +989,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>27</v>
       </c>
@@ -1001,7 +997,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>39</v>
       </c>
@@ -1009,7 +1005,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>12</v>
       </c>
@@ -1017,7 +1013,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>40</v>
       </c>
@@ -1025,7 +1021,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>15</v>
       </c>
@@ -1033,7 +1029,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>16</v>
       </c>
@@ -1041,7 +1037,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>41</v>
       </c>
@@ -1049,7 +1045,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>42</v>
       </c>
@@ -1057,7 +1053,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>28</v>
       </c>
@@ -1065,7 +1061,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>43</v>
       </c>
@@ -1073,7 +1069,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>8</v>
       </c>
@@ -1081,7 +1077,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>44</v>
       </c>
@@ -1089,7 +1085,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>30</v>
       </c>
@@ -1097,7 +1093,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>30</v>
       </c>
@@ -1105,7 +1101,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>30</v>
       </c>
@@ -1113,7 +1109,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>45</v>
       </c>
@@ -1121,7 +1117,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>46</v>
       </c>
@@ -1129,7 +1125,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>47</v>
       </c>
@@ -1137,7 +1133,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>48</v>
       </c>
@@ -1145,7 +1141,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>29</v>
       </c>
@@ -1153,7 +1149,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>49</v>
       </c>
@@ -1161,7 +1157,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>50</v>
       </c>
@@ -1169,7 +1165,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>51</v>
       </c>
